--- a/Assets/Excel/StageRewardSO.xlsx
+++ b/Assets/Excel/StageRewardSO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4F1306-0F05-470B-930B-6F3266A4484F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D50C4F7-906B-4E56-9D85-B609285E22C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{CF32E9D7-666D-4295-A8BB-9CE9D0B7EEA3}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{CF32E9D7-666D-4295-A8BB-9CE9D0B7EEA3}"/>
   </bookViews>
   <sheets>
     <sheet name="StageReward" sheetId="1" r:id="rId1"/>
@@ -344,9 +344,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -366,9 +372,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -406,7 +412,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -512,7 +518,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,7 +660,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -664,6 +670,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABBF67AA-DB15-4EEA-9140-469811A19282}">
   <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -692,17 +706,17 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="1">
+        <v>200</v>
+      </c>
+      <c r="D2" s="1">
         <v>10</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -712,17 +726,17 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
-        <v>20</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="1">
+        <v>240</v>
+      </c>
+      <c r="D3" s="1">
         <v>20</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -732,17 +746,17 @@
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
-        <v>30</v>
-      </c>
-      <c r="D4">
-        <v>30</v>
+      <c r="C4" s="1">
+        <v>290</v>
+      </c>
+      <c r="D4" s="1">
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -752,17 +766,17 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5">
-        <v>40</v>
-      </c>
-      <c r="D5">
-        <v>40</v>
+      <c r="C5" s="1">
+        <v>340</v>
+      </c>
+      <c r="D5" s="1">
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -772,17 +786,17 @@
       <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-      <c r="D6">
-        <v>50</v>
+      <c r="C6" s="1">
+        <v>400</v>
+      </c>
+      <c r="D6" s="1">
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -792,17 +806,17 @@
       <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C7">
-        <v>60</v>
-      </c>
-      <c r="D7">
-        <v>60</v>
+      <c r="C7" s="1">
+        <v>460</v>
+      </c>
+      <c r="D7" s="1">
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -812,17 +826,17 @@
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8">
-        <v>70</v>
-      </c>
-      <c r="D8">
-        <v>70</v>
+      <c r="C8" s="1">
+        <v>520</v>
+      </c>
+      <c r="D8" s="1">
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -832,17 +846,17 @@
       <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9">
-        <v>80</v>
-      </c>
-      <c r="D9">
-        <v>80</v>
+      <c r="C9" s="1">
+        <v>590</v>
+      </c>
+      <c r="D9" s="1">
+        <v>40</v>
       </c>
       <c r="E9">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -852,17 +866,17 @@
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10">
-        <v>90</v>
-      </c>
-      <c r="D10">
-        <v>90</v>
+      <c r="C10" s="1">
+        <v>660</v>
+      </c>
+      <c r="D10" s="1">
+        <v>50</v>
       </c>
       <c r="E10">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -872,17 +886,17 @@
       <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="C11">
-        <v>110</v>
-      </c>
-      <c r="D11">
-        <v>110</v>
-      </c>
-      <c r="E11">
-        <v>110</v>
+      <c r="C11" s="1">
+        <v>1200</v>
+      </c>
+      <c r="D11" s="1">
+        <v>60</v>
+      </c>
+      <c r="E11" s="1">
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -892,17 +906,17 @@
       <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C12">
-        <v>120</v>
-      </c>
-      <c r="D12">
-        <v>120</v>
-      </c>
-      <c r="E12">
-        <v>120</v>
+      <c r="C12" s="1">
+        <v>1300</v>
+      </c>
+      <c r="D12" s="1">
+        <v>70</v>
+      </c>
+      <c r="E12" s="1">
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -912,17 +926,17 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13">
-        <v>130</v>
-      </c>
-      <c r="D13">
-        <v>130</v>
-      </c>
-      <c r="E13">
-        <v>130</v>
+      <c r="C13" s="1">
+        <v>1420</v>
+      </c>
+      <c r="D13" s="1">
+        <v>70</v>
+      </c>
+      <c r="E13" s="1">
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -932,17 +946,17 @@
       <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="C14">
-        <v>140</v>
-      </c>
-      <c r="D14">
-        <v>140</v>
-      </c>
-      <c r="E14">
-        <v>140</v>
+      <c r="C14" s="1">
+        <v>1560</v>
+      </c>
+      <c r="D14" s="1">
+        <v>80</v>
+      </c>
+      <c r="E14" s="1">
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -952,17 +966,17 @@
       <c r="B15" t="s">
         <v>19</v>
       </c>
-      <c r="C15">
-        <v>150</v>
-      </c>
-      <c r="D15">
-        <v>150</v>
-      </c>
-      <c r="E15">
-        <v>150</v>
+      <c r="C15" s="1">
+        <v>1720</v>
+      </c>
+      <c r="D15" s="1">
+        <v>90</v>
+      </c>
+      <c r="E15" s="1">
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -972,17 +986,17 @@
       <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C16">
-        <v>160</v>
-      </c>
-      <c r="D16">
-        <v>160</v>
-      </c>
-      <c r="E16">
-        <v>160</v>
+      <c r="C16" s="1">
+        <v>1900</v>
+      </c>
+      <c r="D16" s="1">
+        <v>100</v>
+      </c>
+      <c r="E16" s="1">
+        <v>40</v>
       </c>
       <c r="F16">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -992,17 +1006,17 @@
       <c r="B17" t="s">
         <v>21</v>
       </c>
-      <c r="C17">
-        <v>170</v>
-      </c>
-      <c r="D17">
-        <v>170</v>
-      </c>
-      <c r="E17">
-        <v>170</v>
+      <c r="C17" s="1">
+        <v>2100</v>
+      </c>
+      <c r="D17" s="1">
+        <v>100</v>
+      </c>
+      <c r="E17" s="1">
+        <v>40</v>
       </c>
       <c r="F17">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1012,17 +1026,17 @@
       <c r="B18" t="s">
         <v>22</v>
       </c>
-      <c r="C18">
-        <v>180</v>
-      </c>
-      <c r="D18">
-        <v>180</v>
-      </c>
-      <c r="E18">
-        <v>180</v>
+      <c r="C18" s="1">
+        <v>2320</v>
+      </c>
+      <c r="D18" s="1">
+        <v>110</v>
+      </c>
+      <c r="E18" s="1">
+        <v>50</v>
       </c>
       <c r="F18">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1032,17 +1046,17 @@
       <c r="B19" t="s">
         <v>23</v>
       </c>
-      <c r="C19">
-        <v>190</v>
-      </c>
-      <c r="D19">
-        <v>190</v>
-      </c>
-      <c r="E19">
-        <v>190</v>
+      <c r="C19" s="1">
+        <v>2560</v>
+      </c>
+      <c r="D19" s="1">
+        <v>120</v>
+      </c>
+      <c r="E19" s="1">
+        <v>60</v>
       </c>
       <c r="F19">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1052,17 +1066,17 @@
       <c r="B20" t="s">
         <v>24</v>
       </c>
-      <c r="C20">
-        <v>210</v>
-      </c>
-      <c r="D20">
-        <v>210</v>
-      </c>
-      <c r="E20">
-        <v>210</v>
-      </c>
-      <c r="F20">
-        <v>210</v>
+      <c r="C20" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D20" s="1">
+        <v>140</v>
+      </c>
+      <c r="E20" s="1">
+        <v>70</v>
+      </c>
+      <c r="F20" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1072,17 +1086,17 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21">
-        <v>220</v>
-      </c>
-      <c r="D21">
-        <v>220</v>
-      </c>
-      <c r="E21">
-        <v>220</v>
-      </c>
-      <c r="F21">
-        <v>220</v>
+      <c r="C21" s="1">
+        <v>3200</v>
+      </c>
+      <c r="D21" s="1">
+        <v>140</v>
+      </c>
+      <c r="E21" s="1">
+        <v>70</v>
+      </c>
+      <c r="F21" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1092,17 +1106,17 @@
       <c r="B22" t="s">
         <v>26</v>
       </c>
-      <c r="C22">
-        <v>230</v>
-      </c>
-      <c r="D22">
-        <v>230</v>
-      </c>
-      <c r="E22">
-        <v>230</v>
-      </c>
-      <c r="F22">
-        <v>230</v>
+      <c r="C22" s="1">
+        <v>3400</v>
+      </c>
+      <c r="D22" s="1">
+        <v>150</v>
+      </c>
+      <c r="E22" s="1">
+        <v>80</v>
+      </c>
+      <c r="F22" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1112,17 +1126,17 @@
       <c r="B23" t="s">
         <v>27</v>
       </c>
-      <c r="C23">
-        <v>240</v>
-      </c>
-      <c r="D23">
-        <v>240</v>
-      </c>
-      <c r="E23">
-        <v>240</v>
-      </c>
-      <c r="F23">
-        <v>240</v>
+      <c r="C23" s="1">
+        <v>3650</v>
+      </c>
+      <c r="D23" s="1">
+        <v>150</v>
+      </c>
+      <c r="E23" s="1">
+        <v>80</v>
+      </c>
+      <c r="F23" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1132,17 +1146,17 @@
       <c r="B24" t="s">
         <v>28</v>
       </c>
-      <c r="C24">
-        <v>250</v>
-      </c>
-      <c r="D24">
-        <v>250</v>
-      </c>
-      <c r="E24">
-        <v>250</v>
-      </c>
-      <c r="F24">
-        <v>250</v>
+      <c r="C24" s="1">
+        <v>3900</v>
+      </c>
+      <c r="D24" s="1">
+        <v>160</v>
+      </c>
+      <c r="E24" s="1">
+        <v>90</v>
+      </c>
+      <c r="F24" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1152,17 +1166,17 @@
       <c r="B25" t="s">
         <v>29</v>
       </c>
-      <c r="C25">
-        <v>260</v>
-      </c>
-      <c r="D25">
-        <v>260</v>
-      </c>
-      <c r="E25">
-        <v>260</v>
-      </c>
-      <c r="F25">
-        <v>260</v>
+      <c r="C25" s="1">
+        <v>4150</v>
+      </c>
+      <c r="D25" s="1">
+        <v>170</v>
+      </c>
+      <c r="E25" s="1">
+        <v>90</v>
+      </c>
+      <c r="F25" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1172,17 +1186,17 @@
       <c r="B26" t="s">
         <v>30</v>
       </c>
-      <c r="C26">
-        <v>270</v>
-      </c>
-      <c r="D26">
-        <v>270</v>
-      </c>
-      <c r="E26">
-        <v>270</v>
-      </c>
-      <c r="F26">
-        <v>270</v>
+      <c r="C26" s="1">
+        <v>4400</v>
+      </c>
+      <c r="D26" s="1">
+        <v>180</v>
+      </c>
+      <c r="E26" s="1">
+        <v>100</v>
+      </c>
+      <c r="F26" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1192,17 +1206,17 @@
       <c r="B27" t="s">
         <v>31</v>
       </c>
-      <c r="C27">
-        <v>280</v>
-      </c>
-      <c r="D27">
-        <v>280</v>
-      </c>
-      <c r="E27">
-        <v>280</v>
-      </c>
-      <c r="F27">
-        <v>280</v>
+      <c r="C27" s="1">
+        <v>4700</v>
+      </c>
+      <c r="D27" s="1">
+        <v>190</v>
+      </c>
+      <c r="E27" s="1">
+        <v>110</v>
+      </c>
+      <c r="F27" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1212,17 +1226,17 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28">
-        <v>290</v>
-      </c>
-      <c r="D28">
-        <v>290</v>
-      </c>
-      <c r="E28">
-        <v>290</v>
-      </c>
-      <c r="F28">
-        <v>290</v>
+      <c r="C28" s="1">
+        <v>5000</v>
+      </c>
+      <c r="D28" s="1">
+        <v>200</v>
+      </c>
+      <c r="E28" s="1">
+        <v>120</v>
+      </c>
+      <c r="F28" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1232,17 +1246,17 @@
       <c r="B29" t="s">
         <v>33</v>
       </c>
-      <c r="C29">
-        <v>310</v>
-      </c>
-      <c r="D29">
-        <v>310</v>
-      </c>
-      <c r="E29">
-        <v>310</v>
-      </c>
-      <c r="F29">
-        <v>310</v>
+      <c r="C29" s="1">
+        <v>6500</v>
+      </c>
+      <c r="D29" s="1">
+        <v>250</v>
+      </c>
+      <c r="E29" s="1">
+        <v>150</v>
+      </c>
+      <c r="F29" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1252,17 +1266,17 @@
       <c r="B30" t="s">
         <v>34</v>
       </c>
-      <c r="C30">
-        <v>320</v>
-      </c>
-      <c r="D30">
-        <v>320</v>
-      </c>
-      <c r="E30">
-        <v>320</v>
-      </c>
-      <c r="F30">
-        <v>320</v>
+      <c r="C30" s="1">
+        <v>7000</v>
+      </c>
+      <c r="D30" s="1">
+        <v>260</v>
+      </c>
+      <c r="E30" s="1">
+        <v>160</v>
+      </c>
+      <c r="F30" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1272,17 +1286,17 @@
       <c r="B31" t="s">
         <v>35</v>
       </c>
-      <c r="C31">
-        <v>330</v>
-      </c>
-      <c r="D31">
-        <v>330</v>
-      </c>
-      <c r="E31">
-        <v>330</v>
-      </c>
-      <c r="F31">
-        <v>330</v>
+      <c r="C31" s="1">
+        <v>7500</v>
+      </c>
+      <c r="D31" s="1">
+        <v>270</v>
+      </c>
+      <c r="E31" s="1">
+        <v>170</v>
+      </c>
+      <c r="F31" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1292,17 +1306,17 @@
       <c r="B32" t="s">
         <v>36</v>
       </c>
-      <c r="C32">
-        <v>340</v>
-      </c>
-      <c r="D32">
-        <v>340</v>
-      </c>
-      <c r="E32">
-        <v>340</v>
-      </c>
-      <c r="F32">
-        <v>340</v>
+      <c r="C32" s="1">
+        <v>8000</v>
+      </c>
+      <c r="D32" s="1">
+        <v>280</v>
+      </c>
+      <c r="E32" s="1">
+        <v>180</v>
+      </c>
+      <c r="F32" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1312,17 +1326,17 @@
       <c r="B33" t="s">
         <v>37</v>
       </c>
-      <c r="C33">
-        <v>350</v>
-      </c>
-      <c r="D33">
-        <v>350</v>
-      </c>
-      <c r="E33">
-        <v>350</v>
-      </c>
-      <c r="F33">
-        <v>350</v>
+      <c r="C33" s="1">
+        <v>8500</v>
+      </c>
+      <c r="D33" s="1">
+        <v>290</v>
+      </c>
+      <c r="E33" s="1">
+        <v>200</v>
+      </c>
+      <c r="F33" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1332,17 +1346,17 @@
       <c r="B34" t="s">
         <v>38</v>
       </c>
-      <c r="C34">
-        <v>360</v>
-      </c>
-      <c r="D34">
-        <v>360</v>
-      </c>
-      <c r="E34">
-        <v>360</v>
-      </c>
-      <c r="F34">
-        <v>360</v>
+      <c r="C34" s="1">
+        <v>9100</v>
+      </c>
+      <c r="D34" s="1">
+        <v>300</v>
+      </c>
+      <c r="E34" s="1">
+        <v>210</v>
+      </c>
+      <c r="F34" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1352,17 +1366,17 @@
       <c r="B35" t="s">
         <v>39</v>
       </c>
-      <c r="C35">
-        <v>370</v>
-      </c>
-      <c r="D35">
-        <v>370</v>
-      </c>
-      <c r="E35">
-        <v>370</v>
-      </c>
-      <c r="F35">
-        <v>370</v>
+      <c r="C35" s="1">
+        <v>9700</v>
+      </c>
+      <c r="D35" s="1">
+        <v>310</v>
+      </c>
+      <c r="E35" s="1">
+        <v>230</v>
+      </c>
+      <c r="F35" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1372,17 +1386,17 @@
       <c r="B36" t="s">
         <v>40</v>
       </c>
-      <c r="C36">
-        <v>380</v>
-      </c>
-      <c r="D36">
-        <v>380</v>
-      </c>
-      <c r="E36">
-        <v>380</v>
-      </c>
-      <c r="F36">
-        <v>380</v>
+      <c r="C36" s="2">
+        <v>10300</v>
+      </c>
+      <c r="D36" s="1">
+        <v>320</v>
+      </c>
+      <c r="E36" s="1">
+        <v>240</v>
+      </c>
+      <c r="F36" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1392,17 +1406,17 @@
       <c r="B37" t="s">
         <v>41</v>
       </c>
-      <c r="C37">
-        <v>390</v>
-      </c>
-      <c r="D37">
-        <v>390</v>
-      </c>
-      <c r="E37">
-        <v>390</v>
-      </c>
-      <c r="F37">
-        <v>390</v>
+      <c r="C37" s="2">
+        <v>11000</v>
+      </c>
+      <c r="D37" s="1">
+        <v>330</v>
+      </c>
+      <c r="E37" s="1">
+        <v>250</v>
+      </c>
+      <c r="F37" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1412,17 +1426,17 @@
       <c r="B38" t="s">
         <v>42</v>
       </c>
-      <c r="C38">
-        <v>410</v>
-      </c>
-      <c r="D38">
-        <v>410</v>
-      </c>
-      <c r="E38">
-        <v>410</v>
-      </c>
-      <c r="F38">
-        <v>410</v>
+      <c r="C38" s="2">
+        <v>15000</v>
+      </c>
+      <c r="D38" s="1">
+        <v>400</v>
+      </c>
+      <c r="E38" s="1">
+        <v>320</v>
+      </c>
+      <c r="F38" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1432,17 +1446,17 @@
       <c r="B39" t="s">
         <v>43</v>
       </c>
-      <c r="C39">
-        <v>420</v>
-      </c>
-      <c r="D39">
-        <v>420</v>
-      </c>
-      <c r="E39">
-        <v>420</v>
-      </c>
-      <c r="F39">
-        <v>420</v>
+      <c r="C39" s="2">
+        <v>16000</v>
+      </c>
+      <c r="D39" s="1">
+        <v>410</v>
+      </c>
+      <c r="E39" s="1">
+        <v>330</v>
+      </c>
+      <c r="F39" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -1452,17 +1466,17 @@
       <c r="B40" t="s">
         <v>44</v>
       </c>
-      <c r="C40">
-        <v>430</v>
-      </c>
-      <c r="D40">
-        <v>430</v>
-      </c>
-      <c r="E40">
-        <v>430</v>
-      </c>
-      <c r="F40">
-        <v>430</v>
+      <c r="C40" s="2">
+        <v>17000</v>
+      </c>
+      <c r="D40" s="1">
+        <v>420</v>
+      </c>
+      <c r="E40" s="1">
+        <v>340</v>
+      </c>
+      <c r="F40" s="1">
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1472,17 +1486,17 @@
       <c r="B41" t="s">
         <v>45</v>
       </c>
-      <c r="C41">
-        <v>440</v>
-      </c>
-      <c r="D41">
-        <v>440</v>
-      </c>
-      <c r="E41">
-        <v>440</v>
-      </c>
-      <c r="F41">
-        <v>440</v>
+      <c r="C41" s="2">
+        <v>18000</v>
+      </c>
+      <c r="D41" s="1">
+        <v>430</v>
+      </c>
+      <c r="E41" s="1">
+        <v>350</v>
+      </c>
+      <c r="F41" s="1">
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1492,17 +1506,17 @@
       <c r="B42" t="s">
         <v>46</v>
       </c>
-      <c r="C42">
-        <v>450</v>
-      </c>
-      <c r="D42">
-        <v>450</v>
-      </c>
-      <c r="E42">
-        <v>450</v>
-      </c>
-      <c r="F42">
-        <v>450</v>
+      <c r="C42" s="2">
+        <v>19500</v>
+      </c>
+      <c r="D42" s="1">
+        <v>440</v>
+      </c>
+      <c r="E42" s="1">
+        <v>370</v>
+      </c>
+      <c r="F42" s="1">
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1512,17 +1526,17 @@
       <c r="B43" t="s">
         <v>47</v>
       </c>
-      <c r="C43">
-        <v>460</v>
-      </c>
-      <c r="D43">
-        <v>460</v>
-      </c>
-      <c r="E43">
-        <v>460</v>
-      </c>
-      <c r="F43">
-        <v>460</v>
+      <c r="C43" s="2">
+        <v>21000</v>
+      </c>
+      <c r="D43" s="1">
+        <v>450</v>
+      </c>
+      <c r="E43" s="1">
+        <v>390</v>
+      </c>
+      <c r="F43" s="1">
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1532,17 +1546,17 @@
       <c r="B44" t="s">
         <v>48</v>
       </c>
-      <c r="C44">
-        <v>470</v>
-      </c>
-      <c r="D44">
-        <v>470</v>
-      </c>
-      <c r="E44">
-        <v>470</v>
-      </c>
-      <c r="F44">
-        <v>470</v>
+      <c r="C44" s="2">
+        <v>22500</v>
+      </c>
+      <c r="D44" s="1">
+        <v>460</v>
+      </c>
+      <c r="E44" s="1">
+        <v>410</v>
+      </c>
+      <c r="F44" s="1">
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1552,17 +1566,17 @@
       <c r="B45" t="s">
         <v>49</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="2">
+        <v>24000</v>
+      </c>
+      <c r="D45" s="1">
         <v>480</v>
       </c>
-      <c r="D45">
-        <v>480</v>
-      </c>
-      <c r="E45">
-        <v>480</v>
-      </c>
-      <c r="F45">
-        <v>480</v>
+      <c r="E45" s="1">
+        <v>430</v>
+      </c>
+      <c r="F45" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1572,17 +1586,17 @@
       <c r="B46" t="s">
         <v>50</v>
       </c>
-      <c r="C46">
-        <v>490</v>
-      </c>
-      <c r="D46">
-        <v>490</v>
-      </c>
-      <c r="E46">
-        <v>490</v>
-      </c>
-      <c r="F46">
-        <v>490</v>
+      <c r="C46" s="2">
+        <v>25500</v>
+      </c>
+      <c r="D46" s="1">
+        <v>500</v>
+      </c>
+      <c r="E46" s="1">
+        <v>450</v>
+      </c>
+      <c r="F46" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">

--- a/Assets/Excel/StageRewardSO.xlsx
+++ b/Assets/Excel/StageRewardSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D50C4F7-906B-4E56-9D85-B609285E22C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9D21B4-578D-409A-BA31-17D466B1AC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{CF32E9D7-666D-4295-A8BB-9CE9D0B7EEA3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CF32E9D7-666D-4295-A8BB-9CE9D0B7EEA3}"/>
   </bookViews>
   <sheets>
     <sheet name="StageReward" sheetId="1" r:id="rId1"/>
@@ -707,13 +707,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="D2" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -727,13 +727,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="1">
-        <v>240</v>
+        <v>720</v>
       </c>
       <c r="D3" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -747,13 +747,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>290</v>
+        <v>870</v>
       </c>
       <c r="D4" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -767,13 +767,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="1">
-        <v>340</v>
+        <v>1020</v>
       </c>
       <c r="D5" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -787,16 +787,16 @@
         <v>10</v>
       </c>
       <c r="C6" s="1">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="D6" s="1">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -807,16 +807,16 @@
         <v>11</v>
       </c>
       <c r="C7" s="1">
-        <v>460</v>
+        <v>1380</v>
       </c>
       <c r="D7" s="1">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -827,16 +827,16 @@
         <v>12</v>
       </c>
       <c r="C8" s="1">
-        <v>520</v>
+        <v>1560</v>
       </c>
       <c r="D8" s="1">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -847,16 +847,16 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>590</v>
+        <v>1770</v>
       </c>
       <c r="D9" s="1">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -867,16 +867,16 @@
         <v>14</v>
       </c>
       <c r="C10" s="1">
-        <v>660</v>
+        <v>1980</v>
       </c>
       <c r="D10" s="1">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -887,16 +887,16 @@
         <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>1200</v>
+        <v>3600</v>
       </c>
       <c r="D11" s="1">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E11" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -907,16 +907,16 @@
         <v>16</v>
       </c>
       <c r="C12" s="1">
-        <v>1300</v>
+        <v>3900</v>
       </c>
       <c r="D12" s="1">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="E12" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -927,16 +927,16 @@
         <v>17</v>
       </c>
       <c r="C13" s="1">
-        <v>1420</v>
+        <v>4260</v>
       </c>
       <c r="D13" s="1">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="E13" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -947,16 +947,16 @@
         <v>18</v>
       </c>
       <c r="C14" s="1">
-        <v>1560</v>
+        <v>4680</v>
       </c>
       <c r="D14" s="1">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="E14" s="1">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -967,16 +967,16 @@
         <v>19</v>
       </c>
       <c r="C15" s="1">
-        <v>1720</v>
+        <v>5160</v>
       </c>
       <c r="D15" s="1">
+        <v>270</v>
+      </c>
+      <c r="E15" s="1">
         <v>90</v>
       </c>
-      <c r="E15" s="1">
-        <v>30</v>
-      </c>
       <c r="F15">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -987,16 +987,16 @@
         <v>20</v>
       </c>
       <c r="C16" s="1">
-        <v>1900</v>
+        <v>5700</v>
       </c>
       <c r="D16" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E16" s="1">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1007,16 +1007,16 @@
         <v>21</v>
       </c>
       <c r="C17" s="1">
-        <v>2100</v>
+        <v>6300</v>
       </c>
       <c r="D17" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E17" s="1">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1027,16 +1027,16 @@
         <v>22</v>
       </c>
       <c r="C18" s="1">
-        <v>2320</v>
+        <v>6960</v>
       </c>
       <c r="D18" s="1">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="E18" s="1">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1047,16 +1047,16 @@
         <v>23</v>
       </c>
       <c r="C19" s="1">
-        <v>2560</v>
+        <v>7680</v>
       </c>
       <c r="D19" s="1">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="E19" s="1">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">

--- a/Assets/Excel/StageRewardSO.xlsx
+++ b/Assets/Excel/StageRewardSO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9D21B4-578D-409A-BA31-17D466B1AC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1290CD08-8CFF-472E-B47F-084C452F53AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CF32E9D7-666D-4295-A8BB-9CE9D0B7EEA3}"/>
+    <workbookView xWindow="10550" yWindow="540" windowWidth="15420" windowHeight="15410" xr2:uid="{CF32E9D7-666D-4295-A8BB-9CE9D0B7EEA3}"/>
   </bookViews>
   <sheets>
     <sheet name="StageReward" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -299,6 +302,10 @@
   </si>
   <si>
     <t>9_09</t>
+  </si>
+  <si>
+    <t>rewardEXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -668,18 +675,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABBF67AA-DB15-4EEA-9140-469811A19282}">
-  <dimension ref="A1:F82"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G82"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -698,8 +706,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -718,8 +729,11 @@
       <c r="F2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -738,8 +752,11 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -758,8 +775,11 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -778,8 +798,11 @@
       <c r="F5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="1">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -798,8 +821,11 @@
       <c r="F6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -818,8 +844,11 @@
       <c r="F7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="1">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -838,8 +867,11 @@
       <c r="F8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="1">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -858,8 +890,11 @@
       <c r="F9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="1">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -878,8 +913,11 @@
       <c r="F10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2001</v>
       </c>
@@ -898,8 +936,11 @@
       <c r="F11">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2002</v>
       </c>
@@ -918,8 +959,11 @@
       <c r="F12">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="1">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>2003</v>
       </c>
@@ -938,8 +982,11 @@
       <c r="F13">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>2004</v>
       </c>
@@ -958,8 +1005,11 @@
       <c r="F14">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="1">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>2005</v>
       </c>
@@ -978,8 +1028,11 @@
       <c r="F15">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="1">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>2006</v>
       </c>
@@ -998,8 +1051,11 @@
       <c r="F16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="1">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>2007</v>
       </c>
@@ -1018,8 +1074,11 @@
       <c r="F17">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="1">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>2008</v>
       </c>
@@ -1038,8 +1097,11 @@
       <c r="F18">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="1">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>2009</v>
       </c>
@@ -1058,8 +1120,11 @@
       <c r="F19">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="1">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>3001</v>
       </c>
@@ -1078,8 +1143,11 @@
       <c r="F20" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="2">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>3002</v>
       </c>
@@ -1098,8 +1166,11 @@
       <c r="F21" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>3003</v>
       </c>
@@ -1118,8 +1189,11 @@
       <c r="F22" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="2">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>3004</v>
       </c>
@@ -1138,8 +1212,11 @@
       <c r="F23" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="2">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>3005</v>
       </c>
@@ -1158,8 +1235,11 @@
       <c r="F24" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="2">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>3006</v>
       </c>
@@ -1178,8 +1258,11 @@
       <c r="F25" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="2">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>3007</v>
       </c>
@@ -1198,8 +1281,11 @@
       <c r="F26" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="2">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>3008</v>
       </c>
@@ -1218,8 +1304,11 @@
       <c r="F27" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="2">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>3009</v>
       </c>
@@ -1238,8 +1327,11 @@
       <c r="F28" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="2">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>4001</v>
       </c>
@@ -1258,8 +1350,11 @@
       <c r="F29" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="2">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>4002</v>
       </c>
@@ -1278,8 +1373,11 @@
       <c r="F30" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="2">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>4003</v>
       </c>
@@ -1298,8 +1396,11 @@
       <c r="F31" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="2">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>4004</v>
       </c>
@@ -1318,8 +1419,11 @@
       <c r="F32" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="2">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>4005</v>
       </c>
@@ -1338,8 +1442,11 @@
       <c r="F33" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="2">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>4006</v>
       </c>
@@ -1358,8 +1465,11 @@
       <c r="F34" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="2">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>4007</v>
       </c>
@@ -1378,8 +1488,11 @@
       <c r="F35" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="2">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>4008</v>
       </c>
@@ -1398,8 +1511,11 @@
       <c r="F36" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36" s="2">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>4009</v>
       </c>
@@ -1418,8 +1534,11 @@
       <c r="F37" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="2">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>5001</v>
       </c>
@@ -1438,8 +1557,11 @@
       <c r="F38" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="2">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>5002</v>
       </c>
@@ -1458,8 +1580,11 @@
       <c r="F39" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="2">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>5003</v>
       </c>
@@ -1478,8 +1603,11 @@
       <c r="F40" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40" s="2">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>5004</v>
       </c>
@@ -1498,8 +1626,11 @@
       <c r="F41" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="2">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>5005</v>
       </c>
@@ -1518,8 +1649,11 @@
       <c r="F42" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="2">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>5006</v>
       </c>
@@ -1538,8 +1672,11 @@
       <c r="F43" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43" s="2">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>5007</v>
       </c>
@@ -1558,8 +1695,11 @@
       <c r="F44" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="2">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>5008</v>
       </c>
@@ -1578,8 +1718,11 @@
       <c r="F45" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45" s="2">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>5009</v>
       </c>
@@ -1598,8 +1741,11 @@
       <c r="F46" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="2">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>6001</v>
       </c>
@@ -1619,7 +1765,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>6002</v>
       </c>
@@ -1639,7 +1785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>6003</v>
       </c>
@@ -1659,7 +1805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>6004</v>
       </c>
@@ -1679,7 +1825,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>6005</v>
       </c>
@@ -1699,7 +1845,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>6006</v>
       </c>
@@ -1719,7 +1865,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>6007</v>
       </c>
@@ -1739,7 +1885,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>6008</v>
       </c>
@@ -1759,7 +1905,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>6009</v>
       </c>
@@ -1779,7 +1925,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>7001</v>
       </c>
@@ -1799,7 +1945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>7002</v>
       </c>
@@ -1819,7 +1965,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>7003</v>
       </c>
@@ -1839,7 +1985,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>7004</v>
       </c>
@@ -1859,7 +2005,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>7005</v>
       </c>
@@ -1879,7 +2025,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>7006</v>
       </c>
@@ -1899,7 +2045,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>7007</v>
       </c>
@@ -1919,7 +2065,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>7008</v>
       </c>
@@ -1939,7 +2085,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>7009</v>
       </c>
@@ -1959,7 +2105,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>8001</v>
       </c>
@@ -1979,7 +2125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>8002</v>
       </c>
@@ -1999,7 +2145,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>8003</v>
       </c>
@@ -2019,7 +2165,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>8004</v>
       </c>
@@ -2039,7 +2185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>8005</v>
       </c>
@@ -2059,7 +2205,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>8006</v>
       </c>
@@ -2079,7 +2225,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>8007</v>
       </c>
@@ -2099,7 +2245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>8008</v>
       </c>
@@ -2119,7 +2265,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>8009</v>
       </c>
@@ -2139,7 +2285,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>9001</v>
       </c>
@@ -2159,7 +2305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>9002</v>
       </c>
@@ -2179,7 +2325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>9003</v>
       </c>
@@ -2199,7 +2345,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>9004</v>
       </c>
@@ -2219,7 +2365,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>9005</v>
       </c>
@@ -2239,7 +2385,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>9006</v>
       </c>
@@ -2259,7 +2405,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>9007</v>
       </c>
@@ -2279,7 +2425,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>9008</v>
       </c>
@@ -2299,7 +2445,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>9009</v>
       </c>
@@ -2322,5 +2468,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>